--- a/Versão5/ABNT/Ontologia_15965_4A.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_4A.xlsx
@@ -8075,7 +8075,7 @@
       </c>
       <c r="B18" s="9">
         <f ca="1">NOW()</f>
-        <v>46138.709736921293</v>
+        <v>46139.357148148149</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>2282</v>

--- a/Versão5/ABNT/Ontologia_15965_4A.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_4A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257CB868-6D9F-4A54-8A3F-45703903E49B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E38EAF-7E94-46C6-BF74-ADB0D134D7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{37D18646-2050-4B3B-8072-5B282545B6D3}"/>
   </bookViews>
@@ -7553,7 +7553,25 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{3612C5C5-E806-48BC-9851-D7419C876F86}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -8120,7 +8138,7 @@
       </c>
       <c r="B18" s="9">
         <f ca="1">NOW()</f>
-        <v>46144.454612384259</v>
+        <v>46146.339664699073</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>2267</v>
@@ -8423,7 +8441,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8576,7 +8594,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8621,7 +8639,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -91906,9 +91924,12 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
